--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6879,0.0978,0.0025,0.1186</t>
-  </si>
-  <si>
-    <t>0.0164,0.0205,0.0038,0.9884</t>
-  </si>
-  <si>
-    <t>0.8902,0.0055,0.0022,0.0933</t>
-  </si>
-  <si>
-    <t>0.0272,0.0046,0.0059,0.9851</t>
-  </si>
-  <si>
-    <t>0.9973,0.0013,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9927,0.0024,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9901,0.0078,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9975,0.0016,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0077,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9914,0.0097,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9977,0.0011,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.4911,0.2426,0.2081,0.0043</t>
-  </si>
-  <si>
-    <t>0.2003,0.0341,0.8420,0.0012</t>
-  </si>
-  <si>
-    <t>0.1773,0.0621,0.8308,0.0009</t>
-  </si>
-  <si>
-    <t>0.0360,0.0108,0.9442,0.0108</t>
-  </si>
-  <si>
-    <t>0.4986,0.0310,0.6283,0.0035</t>
-  </si>
-  <si>
-    <t>0.0113,0.9868,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.0095,0.9896,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.2713,0.8064,0.0171,0.0046</t>
-  </si>
-  <si>
-    <t>0.5137,0.6752,0.0040,0.0017</t>
-  </si>
-  <si>
-    <t>0.0072,0.9888,0.0050,0.0006</t>
-  </si>
-  <si>
-    <t>0.2124,0.0046,0.8366,0.0131</t>
-  </si>
-  <si>
-    <t>0.5927,0.0516,0.2980,0.0885</t>
-  </si>
-  <si>
-    <t>0.0234,0.0166,0.9670,0.0031</t>
-  </si>
-  <si>
-    <t>0.4092,0.0090,0.7325,0.0065</t>
-  </si>
-  <si>
-    <t>0.0224,0.0136,0.9698,0.0016</t>
-  </si>
-  <si>
-    <t>0.0880,0.0025,0.9064,0.0186</t>
-  </si>
-  <si>
-    <t>0.0024,0.0018,0.9953,0.0008</t>
-  </si>
-  <si>
-    <t>0.7488,0.3400,0.0128,0.0029</t>
-  </si>
-  <si>
-    <t>0.7162,0.2987,0.0555,0.0066</t>
-  </si>
-  <si>
-    <t>0.0043,0.0098,0.9852,0.0058</t>
-  </si>
-  <si>
-    <t>0.0367,0.6399,0.5225,0.0009</t>
-  </si>
-  <si>
-    <t>0.9430,0.0287,0.0078,0.0087</t>
-  </si>
-  <si>
-    <t>0.6199,0.0563,0.3839,0.0235</t>
-  </si>
-  <si>
-    <t>0.7009,0.4480,0.0035,0.0028</t>
-  </si>
-  <si>
-    <t>0.0840,0.9063,0.0416,0.0068</t>
-  </si>
-  <si>
-    <t>0.0093,0.8793,0.2554,0.0166</t>
-  </si>
-  <si>
-    <t>0.0699,0.0218,0.8222,0.1282</t>
-  </si>
-  <si>
-    <t>0.0882,0.2070,0.8488,0.0240</t>
-  </si>
-  <si>
-    <t>0.2295,0.0120,0.7942,0.0149</t>
-  </si>
-  <si>
-    <t>0.0183,0.2494,0.9200,0.0015</t>
-  </si>
-  <si>
-    <t>0.0018,0.9895,0.0059,0.0008</t>
-  </si>
-  <si>
-    <t>0.0195,0.1593,0.9200,0.0028</t>
-  </si>
-  <si>
-    <t>0.1547,0.7523,0.0383,0.1927</t>
-  </si>
-  <si>
-    <t>0.0853,0.9083,0.0219,0.0069</t>
-  </si>
-  <si>
-    <t>0.0398,0.9357,0.0452,0.0020</t>
-  </si>
-  <si>
-    <t>0.0173,0.9569,0.0272,0.0152</t>
-  </si>
-  <si>
-    <t>0.0010,0.0475,0.9839,0.0047</t>
-  </si>
-  <si>
-    <t>0.0012,0.1445,0.9915,0.0000</t>
-  </si>
-  <si>
-    <t>0.0490,0.0118,0.9380,0.0064</t>
-  </si>
-  <si>
-    <t>0.0237,0.0032,0.9799,0.0010</t>
-  </si>
-  <si>
-    <t>0.0032,0.0035,0.9900,0.0040</t>
-  </si>
-  <si>
-    <t>0.0489,0.0308,0.9338,0.0021</t>
-  </si>
-  <si>
-    <t>0.9217,0.1037,0.0006,0.0024</t>
-  </si>
-  <si>
-    <t>0.9822,0.0134,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.9806,0.0186,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.0095,0.0304,0.9776,0.0067</t>
-  </si>
-  <si>
-    <t>0.9906,0.0111,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9659,0.0674,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9832,0.0181,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.0033,0.8043,0.9379,0.0007</t>
-  </si>
-  <si>
-    <t>0.0059,0.0617,0.9588,0.0148</t>
-  </si>
-  <si>
-    <t>0.0145,0.1265,0.9545,0.0024</t>
-  </si>
-  <si>
-    <t>0.0016,0.9398,0.8633,0.0009</t>
-  </si>
-  <si>
-    <t>0.0062,0.0035,0.9867,0.0060</t>
-  </si>
-  <si>
-    <t>0.1329,0.7113,0.1619,0.0007</t>
-  </si>
-  <si>
-    <t>0.0054,0.9853,0.0074,0.0002</t>
-  </si>
-  <si>
-    <t>0.8126,0.1126,0.0685,0.0155</t>
-  </si>
-  <si>
-    <t>0.6524,0.3852,0.0299,0.0086</t>
-  </si>
-  <si>
-    <t>0.0254,0.1663,0.8725,0.0045</t>
-  </si>
-  <si>
-    <t>0.0011,0.9170,0.9312,0.0002</t>
-  </si>
-  <si>
-    <t>0.0022,0.9468,0.6484,0.0003</t>
-  </si>
-  <si>
-    <t>0.0004,0.9899,0.3004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9123,0.9537,0.0001</t>
-  </si>
-  <si>
-    <t>0.0236,0.0048,0.0105,0.9828</t>
-  </si>
-  <si>
-    <t>0.0025,0.0388,0.0005,0.9962</t>
-  </si>
-  <si>
-    <t>0.0061,0.0033,0.0020,0.9959</t>
-  </si>
-  <si>
-    <t>0.0210,0.0044,0.0009,0.9911</t>
-  </si>
-  <si>
-    <t>0.0295,0.0056,0.0035,0.9848</t>
-  </si>
-  <si>
-    <t>0.0033,0.0173,0.0005,0.9968</t>
-  </si>
-  <si>
-    <t>0.0005,0.9848,0.5609,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.6765,0.9677,0.0002</t>
-  </si>
-  <si>
-    <t>0.0228,0.2304,0.9089,0.0009</t>
-  </si>
-  <si>
-    <t>0.0037,0.9339,0.5712,0.0009</t>
-  </si>
-  <si>
-    <t>0.0012,0.9803,0.4817,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.8752,0.8448,0.0002</t>
-  </si>
-  <si>
-    <t>0.9930,0.0072,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9860,0.0208,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9904,0.0124,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9932,0.0038,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0036,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9952,0.0033,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9814,0.0314,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9940,0.0062,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0007,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9950,0.0036,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9984,0.0006,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0013,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9947,0.0031,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0022,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9973,0.0007,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.0124,0.0148,0.9565,0.0271</t>
-  </si>
-  <si>
-    <t>0.0744,0.0049,0.9411,0.0065</t>
-  </si>
-  <si>
-    <t>0.8652,0.0034,0.1360,0.0075</t>
-  </si>
-  <si>
-    <t>0.0294,0.0014,0.9754,0.0025</t>
-  </si>
-  <si>
-    <t>0.0347,0.9731,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0214,0.9753,0.0044,0.0012</t>
-  </si>
-  <si>
-    <t>0.0117,0.9832,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.0899,0.9405,0.0032,0.0008</t>
-  </si>
-  <si>
-    <t>0.1812,0.8851,0.0100,0.0020</t>
-  </si>
-  <si>
-    <t>0.0129,0.9807,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.4482,0.7067,0.0033,0.0018</t>
-  </si>
-  <si>
-    <t>0.5774,0.2727,0.1724,0.0430</t>
-  </si>
-  <si>
-    <t>0.3232,0.0125,0.7921,0.0029</t>
-  </si>
-  <si>
-    <t>0.7110,0.0502,0.2100,0.0169</t>
-  </si>
-  <si>
-    <t>0.5751,0.0384,0.4147,0.0241</t>
-  </si>
-  <si>
-    <t>0.0671,0.0697,0.0054,0.9586</t>
-  </si>
-  <si>
-    <t>0.0197,0.9719,0.0262,0.0015</t>
-  </si>
-  <si>
-    <t>0.0066,0.9812,0.0059,0.0042</t>
-  </si>
-  <si>
-    <t>0.0642,0.8813,0.0068,0.0414</t>
-  </si>
-  <si>
-    <t>0.0016,0.8618,0.9209,0.0008</t>
-  </si>
-  <si>
-    <t>0.0239,0.9735,0.0256,0.0002</t>
-  </si>
-  <si>
-    <t>0.8047,0.2808,0.0188,0.0017</t>
-  </si>
-  <si>
-    <t>0.5490,0.6611,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.9143,0.1004,0.0128,0.0023</t>
-  </si>
-  <si>
-    <t>0.9926,0.0020,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9779,0.0038,0.0014,0.0092</t>
-  </si>
-  <si>
-    <t>0.9675,0.0312,0.0031,0.0022</t>
-  </si>
-  <si>
-    <t>0.9951,0.0013,0.0001,0.0010</t>
-  </si>
-  <si>
-    <t>0.9636,0.0261,0.0109,0.0022</t>
-  </si>
-  <si>
-    <t>0.9880,0.0080,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.9948,0.0014,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.0037,0.3799,0.9758,0.0013</t>
-  </si>
-  <si>
-    <t>0.0019,0.7986,0.9529,0.0003</t>
-  </si>
-  <si>
-    <t>0.0054,0.6370,0.9390,0.0014</t>
-  </si>
-  <si>
-    <t>0.0910,0.0169,0.9192,0.0002</t>
-  </si>
-  <si>
-    <t>0.8131,0.0088,0.1406,0.0330</t>
-  </si>
-  <si>
-    <t>0.3989,0.1153,0.5779,0.0095</t>
-  </si>
-  <si>
-    <t>0.1747,0.0208,0.8789,0.0078</t>
-  </si>
-  <si>
-    <t>0.4496,0.4576,0.1204,0.0365</t>
-  </si>
-  <si>
-    <t>0.1330,0.0095,0.0013,0.9349</t>
-  </si>
-  <si>
-    <t>0.0006,0.0015,0.0010,0.9990</t>
-  </si>
-  <si>
-    <t>0.0134,0.0117,0.0024,0.9905</t>
-  </si>
-  <si>
-    <t>0.0177,0.0013,0.0010,0.9934</t>
-  </si>
-  <si>
-    <t>0.0011,0.9889,0.0264,0.0000</t>
-  </si>
-  <si>
-    <t>0.9673,0.0360,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.6184,0.4510,0.0178,0.0045</t>
-  </si>
-  <si>
-    <t>0.9773,0.0273,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.6551,0.5023,0.0095,0.0010</t>
-  </si>
-  <si>
-    <t>0.9893,0.0014,0.0009,0.0027</t>
-  </si>
-  <si>
-    <t>0.6061,0.0347,0.0163,0.3730</t>
-  </si>
-  <si>
-    <t>0.9845,0.0066,0.0041,0.0011</t>
-  </si>
-  <si>
-    <t>0.0041,0.0624,0.9495,0.0433</t>
-  </si>
-  <si>
-    <t>0.8633,0.0003,0.0037,0.1271</t>
-  </si>
-  <si>
-    <t>0.9264,0.0044,0.0049,0.0451</t>
-  </si>
-  <si>
-    <t>0.5613,0.5835,0.0063,0.0021</t>
-  </si>
-  <si>
-    <t>0.8784,0.1222,0.0078,0.0052</t>
-  </si>
-  <si>
-    <t>0.7576,0.2490,0.0420,0.0118</t>
-  </si>
-  <si>
-    <t>0.1500,0.8362,0.0211,0.0165</t>
-  </si>
-  <si>
-    <t>0.8900,0.1020,0.0184,0.0029</t>
-  </si>
-  <si>
-    <t>0.7484,0.2205,0.0379,0.0172</t>
-  </si>
-  <si>
-    <t>0.9911,0.0019,0.0003,0.0027</t>
-  </si>
-  <si>
-    <t>0.9782,0.0103,0.0003,0.0046</t>
-  </si>
-  <si>
-    <t>0.9955,0.0018,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9883,0.0060,0.0014,0.0010</t>
-  </si>
-  <si>
-    <t>0.9898,0.0056,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.9848,0.0086,0.0011,0.0020</t>
-  </si>
-  <si>
-    <t>0.9927,0.0011,0.0002,0.0023</t>
-  </si>
-  <si>
-    <t>0.9878,0.0041,0.0011,0.0023</t>
-  </si>
-  <si>
-    <t>0.5012,0.6324,0.0068,0.0048</t>
-  </si>
-  <si>
-    <t>0.3515,0.8153,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.7092,0.4770,0.0054,0.0005</t>
-  </si>
-  <si>
-    <t>0.5882,0.3528,0.1408,0.0084</t>
-  </si>
-  <si>
-    <t>0.8939,0.2374,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9683,0.0142,0.0034,0.0063</t>
-  </si>
-  <si>
-    <t>0.9807,0.0306,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.8982,0.1055,0.0043,0.0076</t>
-  </si>
-  <si>
-    <t>0.0022,0.0142,0.9937,0.0025</t>
-  </si>
-  <si>
-    <t>0.9169,0.0613,0.0275,0.0064</t>
-  </si>
-  <si>
-    <t>0.0014,0.0074,0.9939,0.0008</t>
-  </si>
-  <si>
-    <t>0.0027,0.0197,0.9945,0.0002</t>
-  </si>
-  <si>
-    <t>0.0152,0.0052,0.9859,0.0004</t>
-  </si>
-  <si>
-    <t>0.0244,0.0458,0.9679,0.0007</t>
-  </si>
-  <si>
-    <t>0.0614,0.0057,0.9603,0.0008</t>
-  </si>
-  <si>
-    <t>0.0232,0.0043,0.9773,0.0012</t>
-  </si>
-  <si>
-    <t>0.0043,0.0174,0.9935,0.0001</t>
-  </si>
-  <si>
-    <t>0.2094,0.0501,0.8306,0.0104</t>
-  </si>
-  <si>
-    <t>0.1528,0.0152,0.9037,0.0009</t>
-  </si>
-  <si>
-    <t>0.6513,0.0278,0.4397,0.0054</t>
-  </si>
-  <si>
-    <t>0.6313,0.0951,0.2985,0.0047</t>
-  </si>
-  <si>
-    <t>0.1531,0.6512,0.2624,0.0141</t>
-  </si>
-  <si>
-    <t>0.4941,0.4808,0.0659,0.0208</t>
-  </si>
-  <si>
-    <t>0.5174,0.1493,0.3798,0.0963</t>
-  </si>
-  <si>
-    <t>0.4613,0.1116,0.5529,0.0108</t>
-  </si>
-  <si>
-    <t>0.1123,0.9306,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.2691,0.8064,0.0069,0.0002</t>
-  </si>
-  <si>
-    <t>0.8603,0.2792,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.9928,0.0086,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.5185,0.6693,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.7181,0.0504,0.0976,0.0954</t>
-  </si>
-  <si>
-    <t>0.7524,0.0083,0.3210,0.0076</t>
-  </si>
-  <si>
-    <t>0.6793,0.0231,0.3764,0.0146</t>
-  </si>
-  <si>
-    <t>0.7078,0.0131,0.3452,0.0131</t>
-  </si>
-  <si>
-    <t>0.8584,0.0088,0.1034,0.0136</t>
-  </si>
-  <si>
-    <t>0.0088,0.0421,0.9592,0.0084</t>
-  </si>
-  <si>
-    <t>0.0407,0.4516,0.8572,0.0119</t>
-  </si>
-  <si>
-    <t>0.0234,0.6237,0.8724,0.0097</t>
-  </si>
-  <si>
-    <t>0.2197,0.0707,0.7890,0.0148</t>
-  </si>
-  <si>
-    <t>0.0138,0.3512,0.7740,0.0092</t>
-  </si>
-  <si>
-    <t>0.9898,0.0046,0.0001,0.0014</t>
-  </si>
-  <si>
-    <t>0.9899,0.0076,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9893,0.0108,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9844,0.0258,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9933,0.0047,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9919,0.0042,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9933,0.0020,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9923,0.0041,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.2269,0.0598,0.7732,0.0098</t>
-  </si>
-  <si>
-    <t>0.7220,0.1328,0.1714,0.0389</t>
-  </si>
-  <si>
-    <t>0.7784,0.0418,0.0219,0.1387</t>
-  </si>
-  <si>
-    <t>0.0022,0.0099,0.9931,0.0006</t>
-  </si>
-  <si>
-    <t>0.0013,0.0562,0.9912,0.0007</t>
-  </si>
-  <si>
-    <t>0.1411,0.0353,0.8378,0.0026</t>
-  </si>
-  <si>
-    <t>0.0063,0.0172,0.9862,0.0030</t>
-  </si>
-  <si>
-    <t>0.0700,0.0285,0.9091,0.0022</t>
-  </si>
-  <si>
-    <t>0.0172,0.0435,0.9757,0.0008</t>
-  </si>
-  <si>
-    <t>0.0098,0.0137,0.9472,0.0370</t>
-  </si>
-  <si>
-    <t>0.4778,0.0489,0.5582,0.0133</t>
-  </si>
-  <si>
-    <t>0.7915,0.0055,0.3134,0.0023</t>
-  </si>
-  <si>
-    <t>0.6824,0.0162,0.3263,0.0351</t>
-  </si>
-  <si>
-    <t>0.8671,0.0061,0.1243,0.0108</t>
-  </si>
-  <si>
-    <t>0.9690,0.0498,0.0010,0.0006</t>
-  </si>
-  <si>
-    <t>0.9926,0.0096,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9907,0.0099,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9867,0.0248,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9918,0.0050,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9974,0.0022,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0021,0.0000,0.0004</t>
-  </si>
-  <si>
-    <t>0.9929,0.0028,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.0643,0.3093,0.6014,0.0091</t>
-  </si>
-  <si>
-    <t>0.0017,0.0368,0.9920,0.0002</t>
-  </si>
-  <si>
-    <t>0.0105,0.5191,0.8931,0.0056</t>
-  </si>
-  <si>
-    <t>0.0320,0.4757,0.4129,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0036,0.9971,0.0010</t>
-  </si>
-  <si>
-    <t>0.3284,0.0119,0.6605,0.0323</t>
-  </si>
-  <si>
-    <t>0.2453,0.0206,0.6736,0.0928</t>
-  </si>
-  <si>
-    <t>0.0221,0.2895,0.5495,0.1865</t>
-  </si>
-  <si>
-    <t>0.8463,0.0011,0.0012,0.2157</t>
-  </si>
-  <si>
-    <t>0.0253,0.0975,0.0037,0.9765</t>
-  </si>
-  <si>
-    <t>0.1065,0.0066,0.0017,0.9556</t>
-  </si>
-  <si>
-    <t>0.0022,0.0007,0.0014,0.9980</t>
-  </si>
-  <si>
-    <t>0.0072,0.0033,0.0038,0.9940</t>
-  </si>
-  <si>
-    <t>0.7254,0.0282,0.0768,0.1696</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.7009,0.0188,0.0026,0.3079</t>
+  </si>
+  <si>
+    <t>0.0095,0.0069,0.0065,0.9913</t>
+  </si>
+  <si>
+    <t>0.9022,0.0131,0.0020,0.0531</t>
+  </si>
+  <si>
+    <t>0.0422,0.0112,0.0010,0.9809</t>
+  </si>
+  <si>
+    <t>0.9964,0.0016,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9931,0.0038,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9835,0.0171,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9970,0.0016,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9924,0.0034,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9960,0.0021,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9957,0.0033,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9953,0.0027,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.7525,0.1165,0.0983,0.0036</t>
+  </si>
+  <si>
+    <t>0.6476,0.0604,0.3704,0.0138</t>
+  </si>
+  <si>
+    <t>0.5561,0.0281,0.5394,0.0053</t>
+  </si>
+  <si>
+    <t>0.0671,0.0024,0.9601,0.0017</t>
+  </si>
+  <si>
+    <t>0.6269,0.1332,0.2639,0.0046</t>
+  </si>
+  <si>
+    <t>0.0696,0.9605,0.0023,0.0003</t>
+  </si>
+  <si>
+    <t>0.0193,0.9812,0.0056,0.0008</t>
+  </si>
+  <si>
+    <t>0.7063,0.3974,0.0148,0.0049</t>
+  </si>
+  <si>
+    <t>0.0496,0.9659,0.0033,0.0004</t>
+  </si>
+  <si>
+    <t>0.0054,0.9923,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.5410,0.0206,0.5559,0.0040</t>
+  </si>
+  <si>
+    <t>0.3046,0.0429,0.6434,0.0149</t>
+  </si>
+  <si>
+    <t>0.0562,0.0382,0.9103,0.0066</t>
+  </si>
+  <si>
+    <t>0.0537,0.0630,0.8907,0.0182</t>
+  </si>
+  <si>
+    <t>0.0195,0.0096,0.9699,0.0062</t>
+  </si>
+  <si>
+    <t>0.0451,0.0020,0.9507,0.0124</t>
+  </si>
+  <si>
+    <t>0.0054,0.0023,0.9885,0.0051</t>
+  </si>
+  <si>
+    <t>0.3357,0.7576,0.0049,0.0015</t>
+  </si>
+  <si>
+    <t>0.6700,0.2361,0.1728,0.0183</t>
+  </si>
+  <si>
+    <t>0.0094,0.0121,0.9738,0.0101</t>
+  </si>
+  <si>
+    <t>0.0375,0.8997,0.0529,0.0008</t>
+  </si>
+  <si>
+    <t>0.8077,0.1317,0.0900,0.0076</t>
+  </si>
+  <si>
+    <t>0.9354,0.0256,0.0215,0.0099</t>
+  </si>
+  <si>
+    <t>0.8717,0.2193,0.0049,0.0012</t>
+  </si>
+  <si>
+    <t>0.2790,0.7439,0.0963,0.0129</t>
+  </si>
+  <si>
+    <t>0.0302,0.7598,0.3071,0.0052</t>
+  </si>
+  <si>
+    <t>0.1139,0.0238,0.9131,0.0036</t>
+  </si>
+  <si>
+    <t>0.1006,0.0894,0.8574,0.0180</t>
+  </si>
+  <si>
+    <t>0.1893,0.0112,0.8387,0.0103</t>
+  </si>
+  <si>
+    <t>0.0068,0.1244,0.9800,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.9953,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0157,0.1226,0.9499,0.0020</t>
+  </si>
+  <si>
+    <t>0.0985,0.4337,0.0026,0.5849</t>
+  </si>
+  <si>
+    <t>0.0117,0.9692,0.0012,0.0099</t>
+  </si>
+  <si>
+    <t>0.0026,0.9811,0.1019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9894,0.0152,0.0088</t>
+  </si>
+  <si>
+    <t>0.0019,0.6363,0.9359,0.0017</t>
+  </si>
+  <si>
+    <t>0.0092,0.0898,0.9757,0.0018</t>
+  </si>
+  <si>
+    <t>0.1540,0.0217,0.8846,0.0019</t>
+  </si>
+  <si>
+    <t>0.0211,0.0013,0.9817,0.0023</t>
+  </si>
+  <si>
+    <t>0.0103,0.1034,0.9173,0.0109</t>
+  </si>
+  <si>
+    <t>0.0060,0.0113,0.9774,0.0076</t>
+  </si>
+  <si>
+    <t>0.9497,0.1141,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9551,0.0092,0.0109,0.0139</t>
+  </si>
+  <si>
+    <t>0.9634,0.0434,0.0026,0.0015</t>
+  </si>
+  <si>
+    <t>0.0008,0.0298,0.9944,0.0019</t>
+  </si>
+  <si>
+    <t>0.9959,0.0014,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9925,0.0041,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9833,0.0276,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9024,0.9684,0.0002</t>
+  </si>
+  <si>
+    <t>0.0283,0.1011,0.9076,0.0175</t>
+  </si>
+  <si>
+    <t>0.0196,0.0089,0.8936,0.1251</t>
+  </si>
+  <si>
+    <t>0.0021,0.7419,0.9680,0.0008</t>
+  </si>
+  <si>
+    <t>0.0046,0.0066,0.9927,0.0006</t>
+  </si>
+  <si>
+    <t>0.0299,0.8722,0.2102,0.0014</t>
+  </si>
+  <si>
+    <t>0.0021,0.9948,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9543,0.0159,0.0184,0.0042</t>
+  </si>
+  <si>
+    <t>0.6297,0.4640,0.0328,0.0052</t>
+  </si>
+  <si>
+    <t>0.1232,0.2165,0.5864,0.0088</t>
+  </si>
+  <si>
+    <t>0.0011,0.9036,0.9384,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.4733,0.9561,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.9936,0.4230,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9679,0.6881,0.0003</t>
+  </si>
+  <si>
+    <t>0.0170,0.0020,0.0176,0.9808</t>
+  </si>
+  <si>
+    <t>0.0031,0.0063,0.0002,0.9978</t>
+  </si>
+  <si>
+    <t>0.0035,0.0022,0.0001,0.9985</t>
+  </si>
+  <si>
+    <t>0.0038,0.0132,0.0003,0.9966</t>
+  </si>
+  <si>
+    <t>0.0302,0.0106,0.0044,0.9826</t>
+  </si>
+  <si>
+    <t>0.0058,0.0091,0.0003,0.9967</t>
+  </si>
+  <si>
+    <t>0.0005,0.9722,0.7689,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.8631,0.9087,0.0004</t>
+  </si>
+  <si>
+    <t>0.0404,0.5940,0.6997,0.0055</t>
+  </si>
+  <si>
+    <t>0.0192,0.4021,0.9100,0.0038</t>
+  </si>
+  <si>
+    <t>0.0006,0.9700,0.8396,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.8693,0.7595,0.0005</t>
+  </si>
+  <si>
+    <t>0.9885,0.0139,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9676,0.0669,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9862,0.0238,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9922,0.0067,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9798,0.0233,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9958,0.0009,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9657,0.0658,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9923,0.0122,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9972,0.0014,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0031,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0013,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9981,0.0007,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0012,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9920,0.0050,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9973,0.0015,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0073,0.0030,0.9870,0.0067</t>
+  </si>
+  <si>
+    <t>0.2462,0.0146,0.8108,0.0043</t>
+  </si>
+  <si>
+    <t>0.5977,0.0017,0.4747,0.0099</t>
+  </si>
+  <si>
+    <t>0.1385,0.0059,0.9307,0.0011</t>
+  </si>
+  <si>
+    <t>0.0508,0.9609,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.0214,0.9757,0.0095,0.0002</t>
+  </si>
+  <si>
+    <t>0.4920,0.6810,0.0040,0.0016</t>
+  </si>
+  <si>
+    <t>0.6441,0.5290,0.0023,0.0014</t>
+  </si>
+  <si>
+    <t>0.0457,0.9647,0.0064,0.0005</t>
+  </si>
+  <si>
+    <t>0.0014,0.9967,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.8520,0.2522,0.0046,0.0014</t>
+  </si>
+  <si>
+    <t>0.6837,0.1755,0.1377,0.0310</t>
+  </si>
+  <si>
+    <t>0.1378,0.0103,0.8976,0.0099</t>
+  </si>
+  <si>
+    <t>0.5431,0.2487,0.1466,0.0200</t>
+  </si>
+  <si>
+    <t>0.3589,0.0172,0.7562,0.0087</t>
+  </si>
+  <si>
+    <t>0.0481,0.3027,0.0050,0.8863</t>
+  </si>
+  <si>
+    <t>0.0260,0.9694,0.0180,0.0011</t>
+  </si>
+  <si>
+    <t>0.0056,0.9842,0.0141,0.0008</t>
+  </si>
+  <si>
+    <t>0.0128,0.9279,0.0124,0.0893</t>
+  </si>
+  <si>
+    <t>0.0053,0.9331,0.6392,0.0004</t>
+  </si>
+  <si>
+    <t>0.0238,0.9747,0.0129,0.0003</t>
+  </si>
+  <si>
+    <t>0.8567,0.2314,0.0091,0.0014</t>
+  </si>
+  <si>
+    <t>0.7061,0.4045,0.0127,0.0010</t>
+  </si>
+  <si>
+    <t>0.9885,0.0082,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9872,0.0041,0.0013,0.0019</t>
+  </si>
+  <si>
+    <t>0.9954,0.0008,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.9877,0.0071,0.0009,0.0013</t>
+  </si>
+  <si>
+    <t>0.9878,0.0012,0.0001,0.0068</t>
+  </si>
+  <si>
+    <t>0.9850,0.0087,0.0009,0.0018</t>
+  </si>
+  <si>
+    <t>0.9948,0.0010,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9953,0.0011,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.0027,0.6987,0.9720,0.0009</t>
+  </si>
+  <si>
+    <t>0.0029,0.4757,0.9768,0.0005</t>
+  </si>
+  <si>
+    <t>0.0069,0.0915,0.9825,0.0002</t>
+  </si>
+  <si>
+    <t>0.0258,0.0206,0.9704,0.0008</t>
+  </si>
+  <si>
+    <t>0.8751,0.0506,0.0279,0.0116</t>
+  </si>
+  <si>
+    <t>0.3738,0.0540,0.6989,0.0302</t>
+  </si>
+  <si>
+    <t>0.1931,0.0042,0.8706,0.0087</t>
+  </si>
+  <si>
+    <t>0.6501,0.1511,0.1524,0.0493</t>
+  </si>
+  <si>
+    <t>0.3474,0.0008,0.0007,0.8624</t>
+  </si>
+  <si>
+    <t>0.0001,0.0033,0.0003,0.9995</t>
+  </si>
+  <si>
+    <t>0.0097,0.0074,0.0022,0.9938</t>
+  </si>
+  <si>
+    <t>0.0800,0.0022,0.0237,0.9380</t>
+  </si>
+  <si>
+    <t>0.0048,0.9696,0.1695,0.0005</t>
+  </si>
+  <si>
+    <t>0.9662,0.0240,0.0059,0.0032</t>
+  </si>
+  <si>
+    <t>0.7714,0.2878,0.0150,0.0055</t>
+  </si>
+  <si>
+    <t>0.9424,0.0086,0.0007,0.0326</t>
+  </si>
+  <si>
+    <t>0.8046,0.3037,0.0087,0.0012</t>
+  </si>
+  <si>
+    <t>0.9906,0.0012,0.0010,0.0022</t>
+  </si>
+  <si>
+    <t>0.8033,0.0035,0.0044,0.2276</t>
+  </si>
+  <si>
+    <t>0.9828,0.0112,0.0029,0.0010</t>
+  </si>
+  <si>
+    <t>0.0029,0.0087,0.9822,0.0269</t>
+  </si>
+  <si>
+    <t>0.9219,0.0003,0.0037,0.0604</t>
+  </si>
+  <si>
+    <t>0.9788,0.0007,0.0019,0.0118</t>
+  </si>
+  <si>
+    <t>0.2690,0.7328,0.0298,0.0029</t>
+  </si>
+  <si>
+    <t>0.7903,0.2221,0.0215,0.0055</t>
+  </si>
+  <si>
+    <t>0.8289,0.1565,0.0436,0.0034</t>
+  </si>
+  <si>
+    <t>0.5275,0.4317,0.0997,0.0328</t>
+  </si>
+  <si>
+    <t>0.8727,0.0742,0.0222,0.0159</t>
+  </si>
+  <si>
+    <t>0.7915,0.1590,0.0434,0.0263</t>
+  </si>
+  <si>
+    <t>0.9975,0.0005,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9912,0.0054,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9811,0.0065,0.0044,0.0028</t>
+  </si>
+  <si>
+    <t>0.9925,0.0009,0.0001,0.0036</t>
+  </si>
+  <si>
+    <t>0.9913,0.0076,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9854,0.0051,0.0016,0.0022</t>
+  </si>
+  <si>
+    <t>0.9916,0.0032,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9947,0.0018,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.7025,0.4002,0.0116,0.0068</t>
+  </si>
+  <si>
+    <t>0.7813,0.4021,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.4817,0.7112,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.0250,0.5238,0.8798,0.0015</t>
+  </si>
+  <si>
+    <t>0.8882,0.2216,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9075,0.0707,0.0052,0.0144</t>
+  </si>
+  <si>
+    <t>0.9644,0.0445,0.0051,0.0004</t>
+  </si>
+  <si>
+    <t>0.3377,0.7800,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.0151,0.0774,0.9740,0.0016</t>
+  </si>
+  <si>
+    <t>0.9666,0.0208,0.0012,0.0065</t>
+  </si>
+  <si>
+    <t>0.0226,0.0038,0.9766,0.0018</t>
+  </si>
+  <si>
+    <t>0.0063,0.0296,0.9890,0.0004</t>
+  </si>
+  <si>
+    <t>0.2655,0.0137,0.7567,0.0296</t>
+  </si>
+  <si>
+    <t>0.0211,0.0449,0.9325,0.0244</t>
+  </si>
+  <si>
+    <t>0.0113,0.0268,0.9837,0.0002</t>
+  </si>
+  <si>
+    <t>0.0548,0.0052,0.9615,0.0005</t>
+  </si>
+  <si>
+    <t>0.0240,0.0134,0.9678,0.0016</t>
+  </si>
+  <si>
+    <t>0.1004,0.0681,0.8739,0.0141</t>
+  </si>
+  <si>
+    <t>0.1164,0.0892,0.8404,0.0012</t>
+  </si>
+  <si>
+    <t>0.7505,0.0326,0.2227,0.0144</t>
+  </si>
+  <si>
+    <t>0.3139,0.6858,0.0137,0.0134</t>
+  </si>
+  <si>
+    <t>0.2900,0.2652,0.4196,0.0085</t>
+  </si>
+  <si>
+    <t>0.1887,0.5252,0.2092,0.0122</t>
+  </si>
+  <si>
+    <t>0.6372,0.0547,0.3527,0.0120</t>
+  </si>
+  <si>
+    <t>0.6203,0.1511,0.2633,0.0827</t>
+  </si>
+  <si>
+    <t>0.8900,0.2405,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.1447,0.9128,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.8445,0.2844,0.0051,0.0005</t>
+  </si>
+  <si>
+    <t>0.9774,0.0268,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.8966,0.2246,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.6190,0.0351,0.4523,0.0072</t>
+  </si>
+  <si>
+    <t>0.8778,0.0059,0.1420,0.0029</t>
+  </si>
+  <si>
+    <t>0.7576,0.0521,0.0971,0.0470</t>
+  </si>
+  <si>
+    <t>0.7152,0.0166,0.3036,0.0140</t>
+  </si>
+  <si>
+    <t>0.6424,0.1738,0.0954,0.0940</t>
+  </si>
+  <si>
+    <t>0.1694,0.0314,0.7924,0.0950</t>
+  </si>
+  <si>
+    <t>0.0576,0.1152,0.9029,0.0053</t>
+  </si>
+  <si>
+    <t>0.0676,0.2816,0.8246,0.0174</t>
+  </si>
+  <si>
+    <t>0.2063,0.2175,0.6696,0.0563</t>
+  </si>
+  <si>
+    <t>0.0198,0.0947,0.9425,0.0009</t>
+  </si>
+  <si>
+    <t>0.9819,0.0170,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9929,0.0082,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9846,0.0114,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9792,0.0302,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9899,0.0081,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9891,0.0181,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9921,0.0055,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9868,0.0146,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.2412,0.1499,0.7060,0.0750</t>
+  </si>
+  <si>
+    <t>0.5686,0.3815,0.1270,0.0263</t>
+  </si>
+  <si>
+    <t>0.8602,0.0217,0.0308,0.0553</t>
+  </si>
+  <si>
+    <t>0.0135,0.0046,0.9881,0.0007</t>
+  </si>
+  <si>
+    <t>0.0046,0.0119,0.9797,0.0045</t>
+  </si>
+  <si>
+    <t>0.0211,0.4426,0.5967,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0062,0.9972,0.0004</t>
+  </si>
+  <si>
+    <t>0.2877,0.0440,0.7313,0.0026</t>
+  </si>
+  <si>
+    <t>0.0061,0.0326,0.9622,0.0136</t>
+  </si>
+  <si>
+    <t>0.0223,0.0470,0.9615,0.0010</t>
+  </si>
+  <si>
+    <t>0.1507,0.1210,0.7631,0.0196</t>
+  </si>
+  <si>
+    <t>0.7433,0.0254,0.1801,0.0496</t>
+  </si>
+  <si>
+    <t>0.5933,0.0109,0.5023,0.0138</t>
+  </si>
+  <si>
+    <t>0.7932,0.0225,0.1670,0.0184</t>
+  </si>
+  <si>
+    <t>0.9839,0.0265,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9881,0.0099,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9956,0.0049,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9937,0.0054,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9928,0.0026,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.9840,0.0236,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9925,0.0066,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9923,0.0058,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0337,0.6385,0.4263,0.0047</t>
+  </si>
+  <si>
+    <t>0.0048,0.1124,0.9682,0.0004</t>
+  </si>
+  <si>
+    <t>0.0196,0.1754,0.9329,0.0044</t>
+  </si>
+  <si>
+    <t>0.1558,0.0518,0.7788,0.0044</t>
+  </si>
+  <si>
+    <t>0.0065,0.0166,0.9875,0.0011</t>
+  </si>
+  <si>
+    <t>0.0816,0.0095,0.6823,0.3628</t>
+  </si>
+  <si>
+    <t>0.2531,0.0240,0.7638,0.0075</t>
+  </si>
+  <si>
+    <t>0.0968,0.5025,0.6373,0.0219</t>
+  </si>
+  <si>
+    <t>0.8183,0.0014,0.0039,0.2049</t>
+  </si>
+  <si>
+    <t>0.0110,0.1165,0.0019,0.9839</t>
+  </si>
+  <si>
+    <t>0.0343,0.0018,0.0012,0.9887</t>
+  </si>
+  <si>
+    <t>0.0132,0.0021,0.0024,0.9930</t>
+  </si>
+  <si>
+    <t>0.0027,0.0036,0.0009,0.9980</t>
+  </si>
+  <si>
+    <t>0.4520,0.0555,0.0166,0.5537</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2144,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2158,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2228,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2270,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2368,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2634,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2970,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3152,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3502,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4202,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4356,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4454,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4597,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4779,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4874,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5045,7 @@
         <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5196,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5336,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5364,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5378,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5434,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
